--- a/Data/Output/result.xlsx
+++ b/Data/Output/result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huyhh1\workspace\uipath\task4\Data\Output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF2FD9B-6749-4D8B-B945-8AA89B6D30C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D799FA45-2BBA-4BFB-AA87-F7226E0B021C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4665" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{2F32FD97-AEF1-4A78-A5FE-C34FB5929895}"/>
   </bookViews>
